--- a/public/exports-with-coowners/29188378.xlsx
+++ b/public/exports-with-coowners/29188378.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">200009921</t>
+          <t xml:space="preserve">200009922</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">200009922</t>
+          <t xml:space="preserve">200009923</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -10114,12 +10114,12 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535912</t>
+          <t xml:space="preserve">311535915</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M135" t="inlineStr">

--- a/public/exports-with-coowners/29188378.xlsx
+++ b/public/exports-with-coowners/29188378.xlsx
@@ -5464,7 +5464,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">200009922</t>
+          <t xml:space="preserve">200009921</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">310001718</t>
+          <t xml:space="preserve">310001719</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535911</t>
+          <t xml:space="preserve">311535915</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535911</t>
+          <t xml:space="preserve">311535915</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535911</t>
+          <t xml:space="preserve">311535915</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M136" t="inlineStr">

--- a/public/exports-with-coowners/29188378.xlsx
+++ b/public/exports-with-coowners/29188378.xlsx
@@ -5539,7 +5539,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">200009923</t>
+          <t xml:space="preserve">200009922</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">310001719</t>
+          <t xml:space="preserve">310001718</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535915</t>
+          <t xml:space="preserve">311535911</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535915</t>
+          <t xml:space="preserve">311535911</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10114,12 +10114,12 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535915</t>
+          <t xml:space="preserve">311535912</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535915</t>
+          <t xml:space="preserve">311535911</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
